--- a/Lab MB1 B/Listado.xlsx
+++ b/Lab MB1 B/Listado.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Documents\gitPrimer-Semestre-25\Lab MB1 B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ubicacion C a D\Documentos\gitPrimer-Semetre-25\Lab MB1 B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D53F5C81-8B48-4B1B-B1EF-ACC9C9A9537D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD2564D-6585-47DA-97FA-201A7939EAA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{38E74753-89FE-4844-B7A9-424ABC4E3D0C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{38E74753-89FE-4844-B7A9-424ABC4E3D0C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -569,31 +569,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ED90767-2529-47D2-9F44-4A0646045BD4}">
   <dimension ref="A1:D60"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="52.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" customWidth="1"/>
+    <col min="1" max="1" width="6.26953125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="52.54296875" customWidth="1"/>
+    <col min="3" max="3" width="19.26953125" customWidth="1"/>
+    <col min="4" max="4" width="16.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="5" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
         <v>3</v>
@@ -605,7 +605,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8">
         <v>1</v>
       </c>
@@ -613,7 +613,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="9"/>
     </row>
-    <row r="7" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="8">
         <v>2</v>
       </c>
@@ -621,7 +621,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="9"/>
     </row>
-    <row r="8" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="8">
         <v>3</v>
       </c>
@@ -629,7 +629,7 @@
       <c r="C8" s="4"/>
       <c r="D8" s="9"/>
     </row>
-    <row r="9" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>4</v>
       </c>
@@ -637,7 +637,7 @@
       <c r="C9" s="4"/>
       <c r="D9" s="9"/>
     </row>
-    <row r="10" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="8">
         <v>5</v>
       </c>
@@ -645,7 +645,7 @@
       <c r="C10" s="4"/>
       <c r="D10" s="9"/>
     </row>
-    <row r="11" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="8">
         <v>6</v>
       </c>
@@ -653,7 +653,7 @@
       <c r="C11" s="4"/>
       <c r="D11" s="9"/>
     </row>
-    <row r="12" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="8">
         <v>7</v>
       </c>
@@ -661,7 +661,7 @@
       <c r="C12" s="4"/>
       <c r="D12" s="9"/>
     </row>
-    <row r="13" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="8">
         <v>8</v>
       </c>
@@ -669,7 +669,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="9"/>
     </row>
-    <row r="14" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8">
         <v>9</v>
       </c>
@@ -677,7 +677,7 @@
       <c r="C14" s="4"/>
       <c r="D14" s="9"/>
     </row>
-    <row r="15" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="8">
         <v>10</v>
       </c>
@@ -685,7 +685,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="9"/>
     </row>
-    <row r="16" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8">
         <v>11</v>
       </c>
@@ -693,7 +693,7 @@
       <c r="C16" s="4"/>
       <c r="D16" s="9"/>
     </row>
-    <row r="17" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="8">
         <v>12</v>
       </c>
@@ -701,7 +701,7 @@
       <c r="C17" s="4"/>
       <c r="D17" s="9"/>
     </row>
-    <row r="18" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8">
         <v>13</v>
       </c>
@@ -709,7 +709,7 @@
       <c r="C18" s="4"/>
       <c r="D18" s="9"/>
     </row>
-    <row r="19" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8">
         <v>14</v>
       </c>
@@ -717,7 +717,7 @@
       <c r="C19" s="4"/>
       <c r="D19" s="9"/>
     </row>
-    <row r="20" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="8">
         <v>15</v>
       </c>
@@ -725,7 +725,7 @@
       <c r="C20" s="4"/>
       <c r="D20" s="9"/>
     </row>
-    <row r="21" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="8">
         <v>16</v>
       </c>
@@ -733,7 +733,7 @@
       <c r="C21" s="4"/>
       <c r="D21" s="9"/>
     </row>
-    <row r="22" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8">
         <v>17</v>
       </c>
@@ -741,7 +741,7 @@
       <c r="C22" s="4"/>
       <c r="D22" s="9"/>
     </row>
-    <row r="23" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="8">
         <v>18</v>
       </c>
@@ -749,7 +749,7 @@
       <c r="C23" s="4"/>
       <c r="D23" s="9"/>
     </row>
-    <row r="24" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="8">
         <v>19</v>
       </c>
@@ -757,7 +757,7 @@
       <c r="C24" s="4"/>
       <c r="D24" s="9"/>
     </row>
-    <row r="25" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="8">
         <v>20</v>
       </c>
@@ -765,7 +765,7 @@
       <c r="C25" s="4"/>
       <c r="D25" s="9"/>
     </row>
-    <row r="26" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="8">
         <v>21</v>
       </c>
@@ -773,7 +773,7 @@
       <c r="C26" s="4"/>
       <c r="D26" s="9"/>
     </row>
-    <row r="27" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="8">
         <v>22</v>
       </c>
@@ -781,7 +781,7 @@
       <c r="C27" s="4"/>
       <c r="D27" s="9"/>
     </row>
-    <row r="28" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="8">
         <v>23</v>
       </c>
@@ -789,7 +789,7 @@
       <c r="C28" s="4"/>
       <c r="D28" s="9"/>
     </row>
-    <row r="29" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="8">
         <v>24</v>
       </c>
@@ -797,7 +797,7 @@
       <c r="C29" s="4"/>
       <c r="D29" s="9"/>
     </row>
-    <row r="30" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="8">
         <v>25</v>
       </c>
@@ -805,7 +805,7 @@
       <c r="C30" s="4"/>
       <c r="D30" s="9"/>
     </row>
-    <row r="31" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="8">
         <v>26</v>
       </c>
@@ -813,7 +813,7 @@
       <c r="C31" s="4"/>
       <c r="D31" s="9"/>
     </row>
-    <row r="32" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="8">
         <v>27</v>
       </c>
@@ -821,7 +821,7 @@
       <c r="C32" s="4"/>
       <c r="D32" s="9"/>
     </row>
-    <row r="33" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="8">
         <v>28</v>
       </c>
@@ -829,7 +829,7 @@
       <c r="C33" s="4"/>
       <c r="D33" s="9"/>
     </row>
-    <row r="34" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="8">
         <v>29</v>
       </c>
@@ -837,7 +837,7 @@
       <c r="C34" s="4"/>
       <c r="D34" s="9"/>
     </row>
-    <row r="35" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="8">
         <v>30</v>
       </c>
@@ -845,7 +845,7 @@
       <c r="C35" s="4"/>
       <c r="D35" s="9"/>
     </row>
-    <row r="36" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="8">
         <v>31</v>
       </c>
@@ -853,7 +853,7 @@
       <c r="C36" s="4"/>
       <c r="D36" s="9"/>
     </row>
-    <row r="37" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="8">
         <v>32</v>
       </c>
@@ -861,7 +861,7 @@
       <c r="C37" s="4"/>
       <c r="D37" s="9"/>
     </row>
-    <row r="38" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="8">
         <v>33</v>
       </c>
@@ -869,7 +869,7 @@
       <c r="C38" s="4"/>
       <c r="D38" s="9"/>
     </row>
-    <row r="39" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="8">
         <v>34</v>
       </c>
@@ -877,7 +877,7 @@
       <c r="C39" s="4"/>
       <c r="D39" s="9"/>
     </row>
-    <row r="40" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="8">
         <v>35</v>
       </c>
@@ -885,7 +885,7 @@
       <c r="C40" s="4"/>
       <c r="D40" s="9"/>
     </row>
-    <row r="41" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="8">
         <v>36</v>
       </c>
@@ -893,7 +893,7 @@
       <c r="C41" s="4"/>
       <c r="D41" s="9"/>
     </row>
-    <row r="42" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="8">
         <v>37</v>
       </c>
@@ -901,7 +901,7 @@
       <c r="C42" s="4"/>
       <c r="D42" s="9"/>
     </row>
-    <row r="43" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="8">
         <v>38</v>
       </c>
@@ -909,7 +909,7 @@
       <c r="C43" s="4"/>
       <c r="D43" s="9"/>
     </row>
-    <row r="44" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="8">
         <v>39</v>
       </c>
@@ -917,7 +917,7 @@
       <c r="C44" s="4"/>
       <c r="D44" s="9"/>
     </row>
-    <row r="45" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="8">
         <v>40</v>
       </c>
@@ -925,7 +925,7 @@
       <c r="C45" s="4"/>
       <c r="D45" s="9"/>
     </row>
-    <row r="46" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="8">
         <v>41</v>
       </c>
@@ -933,7 +933,7 @@
       <c r="C46" s="4"/>
       <c r="D46" s="9"/>
     </row>
-    <row r="47" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="8">
         <v>42</v>
       </c>
@@ -941,7 +941,7 @@
       <c r="C47" s="4"/>
       <c r="D47" s="9"/>
     </row>
-    <row r="48" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="8">
         <v>43</v>
       </c>
@@ -949,7 +949,7 @@
       <c r="C48" s="4"/>
       <c r="D48" s="9"/>
     </row>
-    <row r="49" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="8">
         <v>44</v>
       </c>
@@ -957,7 +957,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="9"/>
     </row>
-    <row r="50" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="8">
         <v>45</v>
       </c>
@@ -965,7 +965,7 @@
       <c r="C50" s="4"/>
       <c r="D50" s="9"/>
     </row>
-    <row r="51" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="8">
         <v>46</v>
       </c>
@@ -973,7 +973,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="9"/>
     </row>
-    <row r="52" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="8">
         <v>47</v>
       </c>
@@ -981,7 +981,7 @@
       <c r="C52" s="4"/>
       <c r="D52" s="9"/>
     </row>
-    <row r="53" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="8">
         <v>48</v>
       </c>
@@ -989,7 +989,7 @@
       <c r="C53" s="4"/>
       <c r="D53" s="9"/>
     </row>
-    <row r="54" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="8">
         <v>49</v>
       </c>
@@ -997,7 +997,7 @@
       <c r="C54" s="4"/>
       <c r="D54" s="9"/>
     </row>
-    <row r="55" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="8">
         <v>50</v>
       </c>
@@ -1005,7 +1005,7 @@
       <c r="C55" s="4"/>
       <c r="D55" s="9"/>
     </row>
-    <row r="56" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="8">
         <v>51</v>
       </c>
@@ -1013,7 +1013,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="9"/>
     </row>
-    <row r="57" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="8">
         <v>52</v>
       </c>
@@ -1021,7 +1021,7 @@
       <c r="C57" s="4"/>
       <c r="D57" s="9"/>
     </row>
-    <row r="58" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="8">
         <v>53</v>
       </c>
@@ -1029,7 +1029,7 @@
       <c r="C58" s="4"/>
       <c r="D58" s="9"/>
     </row>
-    <row r="59" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="8">
         <v>54</v>
       </c>
@@ -1037,7 +1037,7 @@
       <c r="C59" s="4"/>
       <c r="D59" s="9"/>
     </row>
-    <row r="60" spans="1:4" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="10">
         <v>55</v>
       </c>
@@ -1047,6 +1047,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
 </worksheet>
 </file>